--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_09/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_09/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999915484463</v>
+        <v>38.70800876656642</v>
       </c>
       <c r="B2" t="n">
-        <v>119.2449538537646</v>
+        <v>54.90409830079034</v>
       </c>
       <c r="C2" t="n">
-        <v>45.92404103050541</v>
+        <v>35.69238005982186</v>
       </c>
       <c r="D2" t="n">
-        <v>5.62092267533647</v>
+        <v>5.038503516121577</v>
       </c>
       <c r="E2" t="n">
-        <v>4.474628925294981</v>
+        <v>4.80995185845303</v>
       </c>
       <c r="F2" t="n">
-        <v>10.28394380653673</v>
+        <v>3.162802575286086</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01007270758814141</v>
+        <v>0.2774970225805606</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9439069477687688</v>
+        <v>-0.009249881968349308</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.957775865628136</v>
+        <v>-0.5064945972664899</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9817867091511696</v>
+        <v>-0.1882271410107352</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0004655492450835325</v>
+        <v>-0.0003091151523873324</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069666806666</v>
+        <v>-0.49038765810391</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.057416362416352e-05</v>
+        <v>-0.04275112440485923</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999915484463</v>
+        <v>99.99999999998361</v>
       </c>
       <c r="B3" t="n">
-        <v>79.65071656438062</v>
+        <v>193.5979012705137</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92404103050541</v>
+        <v>35.50285316339605</v>
       </c>
       <c r="D3" t="n">
-        <v>5.62092267533647</v>
+        <v>7.077427479050528</v>
       </c>
       <c r="E3" t="n">
-        <v>4.474628925294981</v>
+        <v>4.822889649558634</v>
       </c>
       <c r="F3" t="n">
-        <v>10.28394380653673</v>
+        <v>10.55548786930121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01007270758814141</v>
+        <v>0.009944533777582382</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9439069477687688</v>
+        <v>-0.936147224220262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.957775865628136</v>
+        <v>-0.952046260106683</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9817867091511696</v>
+        <v>-0.9784150579874014</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0004655492450835325</v>
+        <v>-0.0004199326852218695</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069666806666</v>
+        <v>-0.5874999999998832</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.057416362416352e-05</v>
+        <v>-0.0006340363102330659</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>36.98088601252041</v>
+        <v>38.70800876656642</v>
       </c>
       <c r="B4" t="n">
-        <v>108.2328819144914</v>
+        <v>54.02371570681271</v>
       </c>
       <c r="C4" t="n">
-        <v>45.92566615819528</v>
+        <v>35.69238005982186</v>
       </c>
       <c r="D4" t="n">
-        <v>7.600636194497569</v>
+        <v>5.038503516121577</v>
       </c>
       <c r="E4" t="n">
-        <v>4.837563399065901</v>
+        <v>4.824579511232564</v>
       </c>
       <c r="F4" t="n">
-        <v>2.961284512506006</v>
+        <v>3.162802575286086</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3508094557375172</v>
+        <v>0.2774970225805606</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0006271907991581116</v>
+        <v>-0.009249881968349308</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.501766038075934</v>
+        <v>-0.5064945972664899</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1751901378792775</v>
+        <v>-0.1882271410107352</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0003709822406749976</v>
+        <v>-0.0003091151523873324</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4955553752786699</v>
+        <v>-0.49038765810391</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0002451417651571558</v>
+        <v>-0.04275112440485923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>47.5116505910358</v>
+        <v>58.73736926475683</v>
       </c>
       <c r="B5" t="n">
-        <v>92.17084844195799</v>
+        <v>192.8328216184295</v>
       </c>
       <c r="C5" t="n">
-        <v>46.26627181851494</v>
+        <v>45.93215366209433</v>
       </c>
       <c r="D5" t="n">
-        <v>7.031870838131995</v>
+        <v>10.64340618211043</v>
       </c>
       <c r="E5" t="n">
-        <v>4.838023602982125</v>
+        <v>4.9919655519805</v>
       </c>
       <c r="F5" t="n">
-        <v>3.985873289448095</v>
+        <v>5.011570872028669</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1345610440162735</v>
+        <v>0.06446231181247968</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5243838620282378</v>
+        <v>-0.7032411189906236</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7295225308474952</v>
+        <v>-0.814836991102973</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6926607942530241</v>
+        <v>-0.8350705613502547</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1310824564945706</v>
+        <v>-0.1194099440948519</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5654803047996441</v>
+        <v>-0.2935037560113923</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02308639032209239</v>
+        <v>-0.0702065513358463</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>93.1171567689741</v>
+        <v>80.89404049919156</v>
       </c>
       <c r="B6" t="n">
-        <v>134.7856131974909</v>
+        <v>148.9652879885082</v>
       </c>
       <c r="C6" t="n">
-        <v>45.92422282810497</v>
+        <v>46.03344507385086</v>
       </c>
       <c r="D6" t="n">
-        <v>6.991940218009444</v>
+        <v>8.613336883880885</v>
       </c>
       <c r="E6" t="n">
-        <v>4.818534500847832</v>
+        <v>4.999508501978393</v>
       </c>
       <c r="F6" t="n">
-        <v>9.266837127548422</v>
+        <v>7.59483500965819</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01276738416277719</v>
+        <v>0.02028309164497467</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9314542517244754</v>
+        <v>-0.8832848569001162</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9487034357833066</v>
+        <v>-0.9162225978150611</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9762748572720711</v>
+        <v>-0.9521337225279297</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1363579980237654</v>
+        <v>-0.09981874421114324</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5705916541180246</v>
+        <v>-0.4513700385567398</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.68144567143569e-05</v>
+        <v>-0.09335887402305232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88.30221924318033</v>
+        <v>53.86903058020784</v>
       </c>
       <c r="B7" t="n">
-        <v>108.106783164757</v>
+        <v>183.3332733116253</v>
       </c>
       <c r="C7" t="n">
-        <v>45.92629567152576</v>
+        <v>45.90540223914062</v>
       </c>
       <c r="D7" t="n">
-        <v>7.250279041878362</v>
+        <v>10.7064595630964</v>
       </c>
       <c r="E7" t="n">
-        <v>4.775480127994117</v>
+        <v>4.898059268237721</v>
       </c>
       <c r="F7" t="n">
-        <v>8.492323314555799</v>
+        <v>4.504293954582396</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01524212284936999</v>
+        <v>0.0889178690953259</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9203810751190444</v>
+        <v>-0.6172456950528873</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9409357130862901</v>
+        <v>-0.7727135753301432</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9710947208105167</v>
+        <v>-0.7687748923812643</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.05535853200655647</v>
+        <v>-0.06631472802799809</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5346237350550387</v>
+        <v>-0.2588168428839809</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0003360044296617219</v>
+        <v>-0.06409194037499871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37.39791405509384</v>
+        <v>90.33896643781128</v>
       </c>
       <c r="B8" t="n">
-        <v>107.5653736013457</v>
+        <v>164.5020807129355</v>
       </c>
       <c r="C8" t="n">
-        <v>45.92441937910012</v>
+        <v>41.20424753788678</v>
       </c>
       <c r="D8" t="n">
-        <v>7.564958267123948</v>
+        <v>8.194124896385024</v>
       </c>
       <c r="E8" t="n">
-        <v>4.617112105033431</v>
+        <v>4.475906964595361</v>
       </c>
       <c r="F8" t="n">
-        <v>2.994050329446222</v>
+        <v>9.059095378571648</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3358803194563612</v>
+        <v>0.0139422896170062</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.03341680583088886</v>
+        <v>-0.9148516425742599</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.51486787546941</v>
+        <v>-0.9370381063906377</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2110054213382425</v>
+        <v>-0.9684412595384183</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0009163039468749133</v>
+        <v>-0.1205886201896614</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4983244673296601</v>
+        <v>-0.5186651358694054</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.518422470264499e-05</v>
+        <v>-0.2709556960245255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49.89320752130212</v>
+        <v>62.55522021503738</v>
       </c>
       <c r="B9" t="n">
-        <v>106.261319901238</v>
+        <v>169.3235581687335</v>
       </c>
       <c r="C9" t="n">
-        <v>45.92448444700851</v>
+        <v>47.73489015000692</v>
       </c>
       <c r="D9" t="n">
-        <v>6.714677162983086</v>
+        <v>9.54156704415616</v>
       </c>
       <c r="E9" t="n">
-        <v>4.958667587746389</v>
+        <v>4.973361133229206</v>
       </c>
       <c r="F9" t="n">
-        <v>4.214212301809318</v>
+        <v>5.327738600079942</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1117850397496139</v>
+        <v>0.05086081177553003</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5883974406167274</v>
+        <v>-0.7536002034172776</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7607604412127037</v>
+        <v>-0.841130985929465</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7463720830487887</v>
+        <v>-0.8711845821514345</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1126077480001288</v>
+        <v>-0.005536534301756606</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5812939904306771</v>
+        <v>-0.3207059440321414</v>
       </c>
       <c r="M9" t="n">
-        <v>-7.457599330165098e-05</v>
+        <v>-0.2943484857103313</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>38.13315043475555</v>
+        <v>77.30910004498747</v>
       </c>
       <c r="B10" t="n">
-        <v>101.6782440122554</v>
+        <v>173.9289287250631</v>
       </c>
       <c r="C10" t="n">
-        <v>45.92402539802795</v>
+        <v>46.03344507385086</v>
       </c>
       <c r="D10" t="n">
-        <v>7.51540255013308</v>
+        <v>8.613336883880885</v>
       </c>
       <c r="E10" t="n">
-        <v>4.983744427494619</v>
+        <v>4.645023312956572</v>
       </c>
       <c r="F10" t="n">
-        <v>3.055128112089744</v>
+        <v>7.060309822283243</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3115160146754876</v>
+        <v>0.02371548185674094</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.08777263895879714</v>
+        <v>-0.8670538995510059</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5368564932623061</v>
+        <v>-0.9060378980127687</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2694826752032348</v>
+        <v>-0.9431422616220759</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.00558622095800374</v>
+        <v>-0.02869474946625023</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5032064824621595</v>
+        <v>-0.4258273378205357</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.317803851700297e-06</v>
+        <v>-0.09335887402305232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57.79650986306566</v>
+        <v>84.47550531618285</v>
       </c>
       <c r="B11" t="n">
-        <v>112.1012191395428</v>
+        <v>180.56866894948</v>
       </c>
       <c r="C11" t="n">
-        <v>45.92422861762012</v>
+        <v>40.39370297837886</v>
       </c>
       <c r="D11" t="n">
-        <v>9.764411818687737</v>
+        <v>9.129910087602996</v>
       </c>
       <c r="E11" t="n">
-        <v>4.818468746461749</v>
+        <v>4.66710033539734</v>
       </c>
       <c r="F11" t="n">
-        <v>4.7699284450245</v>
+        <v>8.219229215362116</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06915424342954063</v>
+        <v>0.01753602071537782</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.728750914633474</v>
+        <v>-0.8968252473734707</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8282486134223593</v>
+        <v>-0.92492996306631</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8535347043380376</v>
+        <v>-0.9593236047856786</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.008479490942220811</v>
+        <v>-0.1593669253851518</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3177063976609602</v>
+        <v>-0.4768879753778027</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.765010347064427e-05</v>
+        <v>-0.08858317013524381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>46.19277359300875</v>
+        <v>44.4071007588562</v>
       </c>
       <c r="B12" t="n">
-        <v>111.6034637376326</v>
+        <v>175.7643608095642</v>
       </c>
       <c r="C12" t="n">
-        <v>46.16066157754047</v>
+        <v>45.90540223914062</v>
       </c>
       <c r="D12" t="n">
-        <v>6.69843870175787</v>
+        <v>11.01342061493479</v>
       </c>
       <c r="E12" t="n">
-        <v>4.690906220113522</v>
+        <v>2.000830358359709</v>
       </c>
       <c r="F12" t="n">
-        <v>3.773689093347482</v>
+        <v>3.678629164592508</v>
       </c>
       <c r="G12" t="n">
-        <v>0.149251427820106</v>
+        <v>0.1851919111829862</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4834547204463605</v>
+        <v>-0.3220658808987833</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7099746490345863</v>
+        <v>-0.6333865893167724</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6570985784856149</v>
+        <v>-0.5055903328289149</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.000301870523680794</v>
+        <v>-0.001825991849053692</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5567228797858872</v>
+        <v>-0.1914005929068504</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01909292667815785</v>
+        <v>-0.06409194037499871</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>72.0613603711185</v>
+        <v>70.65732388267139</v>
       </c>
       <c r="B13" t="n">
-        <v>103.577209418295</v>
+        <v>164.3819669824231</v>
       </c>
       <c r="C13" t="n">
-        <v>45.92402443338366</v>
+        <v>35.79217584821652</v>
       </c>
       <c r="D13" t="n">
-        <v>9.121651424916013</v>
+        <v>10.68121489442349</v>
       </c>
       <c r="E13" t="n">
-        <v>4.940170014478547</v>
+        <v>4.482764788969772</v>
       </c>
       <c r="F13" t="n">
-        <v>6.36471739045438</v>
+        <v>6.425647912552407</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0310283071198288</v>
+        <v>0.03292927137443152</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8573067861527901</v>
+        <v>-0.8270218177257742</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9000570322222546</v>
+        <v>-0.881818573179227</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9374776157935236</v>
+        <v>-0.9193777101417222</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1007569376821083</v>
+        <v>-0.07765567297674733</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4133033868066162</v>
+        <v>-0.3784334326640336</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.178569070628009e-06</v>
+        <v>-0.06492796627033753</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56.29368879532748</v>
+        <v>63.92684620248623</v>
       </c>
       <c r="B14" t="n">
-        <v>111.7739085760126</v>
+        <v>169.3234617432349</v>
       </c>
       <c r="C14" t="n">
-        <v>45.9242225900861</v>
+        <v>46.24793815416601</v>
       </c>
       <c r="D14" t="n">
-        <v>9.888446929713016</v>
+        <v>9.645288369978699</v>
       </c>
       <c r="E14" t="n">
-        <v>4.994277860029561</v>
+        <v>4.956477567243224</v>
       </c>
       <c r="F14" t="n">
-        <v>4.658704617187294</v>
+        <v>5.457437950208856</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07617409709964137</v>
+        <v>0.04692804043711001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7070294371988948</v>
+        <v>-0.7688249249241604</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8171160506125436</v>
+        <v>-0.8493335559362987</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.83778535389343</v>
+        <v>-0.8816444368682342</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03357951380238954</v>
+        <v>-0.01749185054640974</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.317524863872622</v>
+        <v>-0.3304787791927144</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.678010155923709e-05</v>
+        <v>-0.1423858638093745</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>43.35092249068541</v>
+        <v>45.03980002498233</v>
       </c>
       <c r="B15" t="n">
-        <v>103.2904362027853</v>
+        <v>148.8026227473827</v>
       </c>
       <c r="C15" t="n">
-        <v>46.50450492275135</v>
+        <v>45.80858391772535</v>
       </c>
       <c r="D15" t="n">
-        <v>7.032959244965411</v>
+        <v>11.0314924789553</v>
       </c>
       <c r="E15" t="n">
-        <v>4.991021341605985</v>
+        <v>4.983609085949332</v>
       </c>
       <c r="F15" t="n">
-        <v>3.520489067742425</v>
+        <v>3.731108363820753</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1902700612667188</v>
+        <v>0.1754360981272795</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3765292407846775</v>
+        <v>-0.3499168158187476</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6604801741837139</v>
+        <v>-0.6458235131282556</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5596454401653465</v>
+        <v>-0.5324183520098771</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02178963974740854</v>
+        <v>-0.0107377223278817</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5378528123223644</v>
+        <v>-0.1959085751779991</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.03124778624920334</v>
+        <v>-0.04196203833722253</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>60.25350600723706</v>
+        <v>94.62246980598755</v>
       </c>
       <c r="B16" t="n">
-        <v>106.7085442081429</v>
+        <v>54.88819247269313</v>
       </c>
       <c r="C16" t="n">
-        <v>45.92423254608337</v>
+        <v>40.07197860032439</v>
       </c>
       <c r="D16" t="n">
-        <v>9.511667792101511</v>
+        <v>7.816715042785592</v>
       </c>
       <c r="E16" t="n">
-        <v>4.840732937835256</v>
+        <v>4.528770464073028</v>
       </c>
       <c r="F16" t="n">
-        <v>5.037096246767438</v>
+        <v>9.70697832684113</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0590987342435482</v>
+        <v>0.01193466785910529</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7600682154401556</v>
+        <v>-0.9259431414558735</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8448184822606778</v>
+        <v>-0.9451422871081947</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8755639851600583</v>
+        <v>-0.9738034040536336</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.02303549190294969</v>
+        <v>-0.1937189703117498</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3468944464624957</v>
+        <v>-0.004829052636081318</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.82171298086755e-05</v>
+        <v>-0.01619518507298717</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>73.64147653777522</v>
+        <v>96.76553688655954</v>
       </c>
       <c r="B17" t="n">
-        <v>130.4065061289342</v>
+        <v>181.1779165269246</v>
       </c>
       <c r="C17" t="n">
-        <v>45.92418029945001</v>
+        <v>45.66000804727902</v>
       </c>
       <c r="D17" t="n">
-        <v>9.121651424916013</v>
+        <v>7.138406194344788</v>
       </c>
       <c r="E17" t="n">
-        <v>4.894845638017447</v>
+        <v>4.931448092550336</v>
       </c>
       <c r="F17" t="n">
-        <v>6.580114364399006</v>
+        <v>9.99833885946401</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02874299003410379</v>
+        <v>0.01106821440801948</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8659549767202039</v>
+        <v>-0.9299655850226523</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9053544692100951</v>
+        <v>-0.9476171260937851</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9424407467367051</v>
+        <v>-0.9756189952110333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1301464025673891</v>
+        <v>-0.1412220446434792</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4251069647529479</v>
+        <v>-0.5644544503167367</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.067595778259806e-05</v>
+        <v>-0.008001839378062175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>38.67995887074447</v>
+        <v>88.42403779766032</v>
       </c>
       <c r="B18" t="n">
-        <v>104.445098539357</v>
+        <v>178.6638144511097</v>
       </c>
       <c r="C18" t="n">
-        <v>45.92413506271384</v>
+        <v>48.07738769941636</v>
       </c>
       <c r="D18" t="n">
-        <v>7.600636194497569</v>
+        <v>7.386724417890846</v>
       </c>
       <c r="E18" t="n">
-        <v>3.718762009110067</v>
+        <v>4.90940642803762</v>
       </c>
       <c r="F18" t="n">
-        <v>3.121601975357109</v>
+        <v>8.647539139904403</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2951212683559078</v>
+        <v>0.01493413171441076</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1253962326935985</v>
+        <v>-0.9095866290441598</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5522572063325251</v>
+        <v>-0.9335138467017208</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3092484703710763</v>
+        <v>-0.9658478855897299</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.04071973738013342</v>
+        <v>-0.02272491908443011</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.506837324369499</v>
+        <v>-0.5050212693083297</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.414657995447877e-05</v>
+        <v>-0.09863560033351003</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>44.20892542162253</v>
+        <v>39.94831207880893</v>
       </c>
       <c r="B19" t="n">
-        <v>111.6034637376326</v>
+        <v>53.47593089709244</v>
       </c>
       <c r="C19" t="n">
-        <v>45.94572373205652</v>
+        <v>35.7461335094947</v>
       </c>
       <c r="D19" t="n">
-        <v>7.057646029777744</v>
+        <v>5.033521911359243</v>
       </c>
       <c r="E19" t="n">
-        <v>4.921448691298051</v>
+        <v>4.843923274429297</v>
       </c>
       <c r="F19" t="n">
-        <v>3.604149217734418</v>
+        <v>3.316463281935151</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1765656120459317</v>
+        <v>0.2460482604900534</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4116812863512925</v>
+        <v>-0.09773437485993561</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6764776389685357</v>
+        <v>-0.5421313656960206</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5923389344149353</v>
+        <v>-0.283177598171824</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.04051180851057812</v>
+        <v>-0.08085446402248726</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5435500049646698</v>
+        <v>-0.4420158289264518</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.002968764822469701</v>
+        <v>-0.05469633544326807</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>69.33101472062869</v>
+        <v>39.05169171170206</v>
       </c>
       <c r="B20" t="n">
-        <v>100.5188156690147</v>
+        <v>54.02371570681271</v>
       </c>
       <c r="C20" t="n">
-        <v>47.52117707934379</v>
+        <v>35.69238005982186</v>
       </c>
       <c r="D20" t="n">
-        <v>8.944285235564337</v>
+        <v>5.038503516121577</v>
       </c>
       <c r="E20" t="n">
-        <v>4.713755703919689</v>
+        <v>4.824579511232564</v>
       </c>
       <c r="F20" t="n">
-        <v>6.019199436677064</v>
+        <v>3.204781608978125</v>
       </c>
       <c r="G20" t="n">
-        <v>0.03561493346670854</v>
+        <v>0.2682874660217578</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8404307946951425</v>
+        <v>-0.03489721582879812</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8899197806577838</v>
+        <v>-0.516730692082308</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9275057528164545</v>
+        <v>-0.2160504101924954</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.04489101284172137</v>
+        <v>-0.0227502830050841</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3929075144106179</v>
+        <v>-0.4769840232436198</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.003200155912744972</v>
+        <v>-0.04275112440485923</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>76.31345440700966</v>
+        <v>45.91235050748448</v>
       </c>
       <c r="B21" t="n">
-        <v>95.50175960298994</v>
+        <v>164.4863178439753</v>
       </c>
       <c r="C21" t="n">
-        <v>45.92458222338181</v>
+        <v>46.44804728374265</v>
       </c>
       <c r="D21" t="n">
-        <v>8.480272437700608</v>
+        <v>10.85364506015195</v>
       </c>
       <c r="E21" t="n">
-        <v>4.856905459449665</v>
+        <v>4.969943266600348</v>
       </c>
       <c r="F21" t="n">
-        <v>6.849055751675565</v>
+        <v>3.801560576810399</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02526160150343042</v>
+        <v>0.1630073964872874</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8791402354203606</v>
+        <v>-0.3858839466621648</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9136556235318539</v>
+        <v>-0.662102466874578</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9498205454049979</v>
+        <v>-0.5665083667822979</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.05140106297593919</v>
+        <v>-0.002887991008140084</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4450668257529867</v>
+        <v>-0.2021254973658269</v>
       </c>
       <c r="M21" t="n">
-        <v>-8.868883472007149e-05</v>
+        <v>-0.1881250934268901</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>42.36234805623306</v>
+        <v>68.14017292668797</v>
       </c>
       <c r="B22" t="n">
-        <v>103.7737165141829</v>
+        <v>173.1045540986532</v>
       </c>
       <c r="C22" t="n">
-        <v>45.97994563820659</v>
+        <v>45.9328859123066</v>
       </c>
       <c r="D22" t="n">
-        <v>7.216039865986221</v>
+        <v>10.60173752798271</v>
       </c>
       <c r="E22" t="n">
-        <v>4.974972460331739</v>
+        <v>4.789930391150338</v>
       </c>
       <c r="F22" t="n">
-        <v>3.43179692575226</v>
+        <v>6.129089030987179</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2078603160569746</v>
+        <v>0.03754114913930807</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3323916538594908</v>
+        <v>-0.8077233763866175</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6407190681150478</v>
+        <v>-0.870706181049686</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5177157494229929</v>
+        <v>-0.9072421189394099</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.03417157469570602</v>
+        <v>-0.2362494571619641</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5312886168036128</v>
+        <v>-0.3604987321026517</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.006964701406456292</v>
+        <v>-0.07037392281293797</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>52.61091272372145</v>
+        <v>51.0299597786355</v>
       </c>
       <c r="B23" t="n">
-        <v>105.8680226381182</v>
+        <v>181.7806125718294</v>
       </c>
       <c r="C23" t="n">
-        <v>45.92448444700851</v>
+        <v>46.44061299368714</v>
       </c>
       <c r="D23" t="n">
-        <v>6.69843870175787</v>
+        <v>10.60173752798271</v>
       </c>
       <c r="E23" t="n">
-        <v>4.958667587746389</v>
+        <v>4.789930391150338</v>
       </c>
       <c r="F23" t="n">
-        <v>4.559030280280904</v>
+        <v>4.226729991571105</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09177523591164345</v>
+        <v>0.1089497653526302</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6478150166505453</v>
+        <v>-0.5509765056871255</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7894377584205603</v>
+        <v>-0.7404102474552777</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7937770868710564</v>
+        <v>-0.7141344219731157</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1913616568826845</v>
+        <v>-0.0216631180145984</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5993397214240052</v>
+        <v>-0.238588463422778</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.457599330165098e-05</v>
+        <v>-0.1864258271284895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>39.22380089761067</v>
+        <v>48.44280875526687</v>
       </c>
       <c r="B24" t="n">
-        <v>96.39946428889351</v>
+        <v>165.7772334004712</v>
       </c>
       <c r="C24" t="n">
-        <v>45.92441932696278</v>
+        <v>40.01635814717096</v>
       </c>
       <c r="D24" t="n">
-        <v>7.411206874290962</v>
+        <v>11.50897368137183</v>
       </c>
       <c r="E24" t="n">
-        <v>4.855823394615916</v>
+        <v>4.863432741889714</v>
       </c>
       <c r="F24" t="n">
-        <v>3.143173705884981</v>
+        <v>4.076934246717956</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2793228425779005</v>
+        <v>0.1333633304552594</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1611293477498977</v>
+        <v>-0.4756642219295715</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5671167445335218</v>
+        <v>-0.7037741526997136</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.34658442017791</v>
+        <v>-0.6485841508260298</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.004749929497612794</v>
+        <v>-0.004067049162275583</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5104484691363991</v>
+        <v>-0.2201550123812764</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.517669930604005e-05</v>
+        <v>-0.003680583113465918</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>40.70105673543559</v>
+        <v>98.86966326580732</v>
       </c>
       <c r="B25" t="n">
-        <v>100.4254719379801</v>
+        <v>166.6697503135699</v>
       </c>
       <c r="C25" t="n">
-        <v>46.20241746476898</v>
+        <v>46.48745270267801</v>
       </c>
       <c r="D25" t="n">
-        <v>7.267672794489584</v>
+        <v>7.13463116728373</v>
       </c>
       <c r="E25" t="n">
-        <v>4.560567116733221</v>
+        <v>4.930997068494118</v>
       </c>
       <c r="F25" t="n">
-        <v>3.274015535858397</v>
+        <v>10.40693365738904</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2422776946848207</v>
+        <v>0.01032972766285402</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2483249834605849</v>
+        <v>-0.9340540717262086</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6040295071597374</v>
+        <v>-0.9505211282295641</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4353338588796248</v>
+        <v>-0.9774757875147834</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.009461009375866665</v>
+        <v>-0.2156159127882817</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.520257539463078</v>
+        <v>-0.5794463507688772</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.02089886619835237</v>
+        <v>-0.1971320463264027</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40.04277128518034</v>
+        <v>41.08085836304464</v>
       </c>
       <c r="B26" t="n">
-        <v>105.9237800374981</v>
+        <v>54.03921449983434</v>
       </c>
       <c r="C26" t="n">
-        <v>45.9243694518175</v>
+        <v>45.67425106851655</v>
       </c>
       <c r="D26" t="n">
-        <v>7.518433037051423</v>
+        <v>5.117562093795136</v>
       </c>
       <c r="E26" t="n">
-        <v>4.967600102713606</v>
+        <v>4.677724887161811</v>
       </c>
       <c r="F26" t="n">
-        <v>3.241859992480274</v>
+        <v>3.492400818289035</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2582641968065514</v>
+        <v>0.2214365357051416</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2108578212595385</v>
+        <v>-0.1676313754223497</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5879977619311079</v>
+        <v>-0.5706274597717625</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3975484772173447</v>
+        <v>-0.3555761186043382</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.05277117120727829</v>
+        <v>-0.2578080732057216</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5158864832714228</v>
+        <v>-0.6814175965305775</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.797782300889509e-05</v>
+        <v>-0.01125738708949775</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>85.12372519710104</v>
+        <v>75.99112534474591</v>
       </c>
       <c r="B27" t="n">
-        <v>112.274587232645</v>
+        <v>173.9289287250631</v>
       </c>
       <c r="C27" t="n">
-        <v>45.92418029945001</v>
+        <v>46.03344507385086</v>
       </c>
       <c r="D27" t="n">
-        <v>9.402684293651919</v>
+        <v>8.613336883880885</v>
       </c>
       <c r="E27" t="n">
-        <v>4.821439545251345</v>
+        <v>4.955236341075946</v>
       </c>
       <c r="F27" t="n">
-        <v>8.3320398717418</v>
+        <v>6.869886124457843</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01744256748623775</v>
+        <v>0.0251760948570651</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9114039613867331</v>
+        <v>-0.8603036244298508</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9346407597502289</v>
+        <v>-0.9018884158515581</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9666937169900197</v>
+        <v>-0.9392930400083364</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.3821337997791945</v>
+        <v>-0.002541476269429565</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5108801628946261</v>
+        <v>-0.4164367680813147</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.067595778259806e-05</v>
+        <v>-0.09335887402305232</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>40.88063159060455</v>
+        <v>40.62679205844515</v>
       </c>
       <c r="B28" t="n">
-        <v>101.4833728821364</v>
+        <v>60.252686954167</v>
       </c>
       <c r="C28" t="n">
-        <v>45.92546088135146</v>
+        <v>35.65405087146446</v>
       </c>
       <c r="D28" t="n">
-        <v>7.589463750525012</v>
+        <v>5.168038440672821</v>
       </c>
       <c r="E28" t="n">
-        <v>4.959273312424537</v>
+        <v>2.254777059832275</v>
       </c>
       <c r="F28" t="n">
-        <v>3.338198905441535</v>
+        <v>3.421833026588124</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2387203441686697</v>
+        <v>0.2309077291053655</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2577536521507248</v>
+        <v>-0.1398203721333095</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6080261849639538</v>
+        <v>-0.5590856346103845</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.444657166930538</v>
+        <v>-0.3268118216482304</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.09037517652199197</v>
+        <v>-0.04172899219633205</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5214499276318388</v>
+        <v>-0.6787215778470181</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.00021551252604692</v>
+        <v>-0.03423352699210375</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95.16351650931681</v>
+        <v>40.34533805866037</v>
       </c>
       <c r="B29" t="n">
-        <v>113.1658489185336</v>
+        <v>56.95868985448669</v>
       </c>
       <c r="C29" t="n">
-        <v>45.92404103050541</v>
+        <v>40.13316060473471</v>
       </c>
       <c r="D29" t="n">
-        <v>6.899662273076007</v>
+        <v>5.00369543449015</v>
       </c>
       <c r="E29" t="n">
-        <v>4.933979171323833</v>
+        <v>2.055450463900671</v>
       </c>
       <c r="F29" t="n">
-        <v>9.612054691323527</v>
+        <v>3.370155069395305</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01188513132790734</v>
+        <v>0.2369836617401016</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9355094995291846</v>
+        <v>-0.1219960402093894</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9516058913731265</v>
+        <v>-0.5517497980238615</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9781070189750268</v>
+        <v>-0.3082251532874599</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1794650846168969</v>
+        <v>-0.07579791817042719</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5858781040709272</v>
+        <v>-0.6770504447232959</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.057416362416352e-05</v>
+        <v>-0.02996113606530987</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>62.25745064702308</v>
+        <v>51.30414722043997</v>
       </c>
       <c r="B30" t="n">
-        <v>106.7703488855345</v>
+        <v>165.7772334004712</v>
       </c>
       <c r="C30" t="n">
-        <v>45.92566615290566</v>
+        <v>40.01635814717096</v>
       </c>
       <c r="D30" t="n">
-        <v>9.471913496826541</v>
+        <v>11.35002387084059</v>
       </c>
       <c r="E30" t="n">
-        <v>4.840732937835256</v>
+        <v>4.865064837548403</v>
       </c>
       <c r="F30" t="n">
-        <v>5.227856498098413</v>
+        <v>4.320166247997795</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05251689025972872</v>
+        <v>0.1072056425174665</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7818457111673499</v>
+        <v>-0.5576024934291373</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8565818716398234</v>
+        <v>-0.7435862965822432</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8902983996973307</v>
+        <v>-0.7196485574802245</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.02324885309304437</v>
+        <v>-0.01378687026884361</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.3509112619233883</v>
+        <v>-0.2405420489456347</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0002451410016636457</v>
+        <v>-0.003680583113465918</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>84.3803203524196</v>
+        <v>49.67481186441836</v>
       </c>
       <c r="B31" t="n">
-        <v>102.3263147464516</v>
+        <v>180.1093886519287</v>
       </c>
       <c r="C31" t="n">
-        <v>45.92566626955426</v>
+        <v>46.00726633048034</v>
       </c>
       <c r="D31" t="n">
-        <v>7.559380174233882</v>
+        <v>10.63721675730253</v>
       </c>
       <c r="E31" t="n">
-        <v>4.984283939511388</v>
+        <v>4.362586933371481</v>
       </c>
       <c r="F31" t="n">
-        <v>7.909755905858014</v>
+        <v>4.087447246689183</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01778762126145273</v>
+        <v>0.1205026918172003</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9094116020151222</v>
+        <v>-0.513907076216976</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9334438328528851</v>
+        <v>-0.7222941039598727</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9657248588659013</v>
+        <v>-0.6823716670461182</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.02489945721224054</v>
+        <v>-0.001421382125063448</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5053268768672802</v>
+        <v>-0.2289330345339808</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0002451578384825681</v>
+        <v>-0.0873751612526491</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>78.42008634154936</v>
+        <v>57.11308726815663</v>
       </c>
       <c r="B32" t="n">
-        <v>112.1768816368316</v>
+        <v>181.4110544518239</v>
       </c>
       <c r="C32" t="n">
-        <v>45.92418029945001</v>
+        <v>40.13772794564289</v>
       </c>
       <c r="D32" t="n">
-        <v>9.402684293651919</v>
+        <v>10.8551529060516</v>
       </c>
       <c r="E32" t="n">
-        <v>4.821439545251345</v>
+        <v>4.870313383781966</v>
       </c>
       <c r="F32" t="n">
-        <v>7.306347823031166</v>
+        <v>4.838862543136885</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02311672100754534</v>
+        <v>0.07151763156155316</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8880485550177522</v>
+        <v>-0.6777556031336426</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9192388414638929</v>
+        <v>-0.8020466338681919</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9546323314640816</v>
+        <v>-0.8160088030604435</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.2648749422919436</v>
+        <v>-0.008732409785214782</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4608035131993173</v>
+        <v>-0.2819307467856159</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.067595778259806e-05</v>
+        <v>-0.03098878776964936</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>42.78841130420132</v>
+        <v>52.46962588155688</v>
       </c>
       <c r="B33" t="n">
-        <v>100.4254719379801</v>
+        <v>168.6581959258864</v>
       </c>
       <c r="C33" t="n">
-        <v>45.92551188871558</v>
+        <v>42.29704478675746</v>
       </c>
       <c r="D33" t="n">
-        <v>7.185571892057524</v>
+        <v>10.88467733046363</v>
       </c>
       <c r="E33" t="n">
-        <v>4.834827539858183</v>
+        <v>4.953548633987101</v>
       </c>
       <c r="F33" t="n">
-        <v>3.470607910637561</v>
+        <v>4.45927768944394</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2000401568564873</v>
+        <v>0.09867378978749812</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3519093943648046</v>
+        <v>-0.5858243531633345</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6494124756319583</v>
+        <v>-0.7576694966779703</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5363733187193166</v>
+        <v>-0.7431303825893056</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.03615682289756352</v>
+        <v>-0.0008290231441689076</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5341177031784465</v>
+        <v>-0.2488460844060927</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0002228748244919106</v>
+        <v>-0.2079123074489301</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>51.3229869063012</v>
+        <v>46.95748437462601</v>
       </c>
       <c r="B34" t="n">
-        <v>108.7543564756326</v>
+        <v>182.2817515980018</v>
       </c>
       <c r="C34" t="n">
-        <v>45.92645400067379</v>
+        <v>46.43451457239182</v>
       </c>
       <c r="D34" t="n">
-        <v>6.690733907843385</v>
+        <v>10.80922986967968</v>
       </c>
       <c r="E34" t="n">
-        <v>4.313294469367717</v>
+        <v>4.687461886146775</v>
       </c>
       <c r="F34" t="n">
-        <v>4.361845051049885</v>
+        <v>3.885085402883646</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1007204982776225</v>
+        <v>0.1495474144434308</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6211302161920205</v>
+        <v>-0.4255478112955592</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7765520695215989</v>
+        <v>-0.680354358974116</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7727762292588574</v>
+        <v>-0.6033442983862137</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.09780289579770643</v>
+        <v>-0.007531010496900649</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5797491456453383</v>
+        <v>-0.2095720761692104</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0003588573345373297</v>
+        <v>-0.185031902260988</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>84.38418446640252</v>
+        <v>41.83615823109528</v>
       </c>
       <c r="B35" t="n">
-        <v>102.2405841845637</v>
+        <v>67.87003090756573</v>
       </c>
       <c r="C35" t="n">
-        <v>45.92561806406516</v>
+        <v>35.87847182957685</v>
       </c>
       <c r="D35" t="n">
-        <v>7.559380174233882</v>
+        <v>5.002343057760902</v>
       </c>
       <c r="E35" t="n">
-        <v>4.845461097139376</v>
+        <v>4.800015523700527</v>
       </c>
       <c r="F35" t="n">
-        <v>7.910364698555211</v>
+        <v>3.556952385181635</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01778486290519845</v>
+        <v>0.2064437403264849</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9094233797998347</v>
+        <v>-0.2115308163828913</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9334517489278257</v>
+        <v>-0.589110010348936</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9657307400747623</v>
+        <v>-0.4003983955098702</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.02500288084868945</v>
+        <v>-0.0593481265896</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.505355742068177</v>
+        <v>-0.6859021894971282</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0002381999569403529</v>
+        <v>-0.08410485101707887</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>79.65200371204016</v>
+        <v>42.26945147836056</v>
       </c>
       <c r="B36" t="n">
-        <v>95.08960986314628</v>
+        <v>52.81722515911331</v>
       </c>
       <c r="C36" t="n">
-        <v>45.93084308673761</v>
+        <v>35.73161435222268</v>
       </c>
       <c r="D36" t="n">
-        <v>9.559801351734281</v>
+        <v>5.007474191910978</v>
       </c>
       <c r="E36" t="n">
-        <v>4.813345387111902</v>
+        <v>4.802785585457674</v>
       </c>
       <c r="F36" t="n">
-        <v>7.514709333758771</v>
+        <v>3.611715166853326</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02192331759044492</v>
+        <v>0.198526737485609</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8929064062237434</v>
+        <v>-0.2352378948417344</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9223643034353927</v>
+        <v>-0.5991914649181564</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9572127515311776</v>
+        <v>-0.4242446702890513</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.3097346824714695</v>
+        <v>-0.08461610174168377</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.4700060218584085</v>
+        <v>-0.6884748681527658</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0009923690255435455</v>
+        <v>-0.05146985604948404</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>38.35873326031714</v>
+        <v>89.37676900759507</v>
       </c>
       <c r="B37" t="n">
-        <v>110.6115945537056</v>
+        <v>74.60177445811684</v>
       </c>
       <c r="C37" t="n">
-        <v>45.92565541665721</v>
+        <v>40.13184631139456</v>
       </c>
       <c r="D37" t="n">
-        <v>7.518433037051423</v>
+        <v>7.996115806999892</v>
       </c>
       <c r="E37" t="n">
-        <v>4.82904075539934</v>
+        <v>4.528770464073028</v>
       </c>
       <c r="F37" t="n">
-        <v>3.077197155220632</v>
+        <v>8.8283480826596</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3045400581978215</v>
+        <v>0.014419161445943</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1035978734051325</v>
+        <v>-0.912278518544825</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5433205666925883</v>
+        <v>-0.9353209969160122</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.286287745072535</v>
+        <v>-0.9671817055968861</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.01189987372436234</v>
+        <v>-0.0267386779528399</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.5047043664060015</v>
+        <v>-0.5118094791791148</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0002435913535568472</v>
+        <v>-0.02966542006377609</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>65.27088374744837</v>
+        <v>47.79090273501999</v>
       </c>
       <c r="B38" t="n">
-        <v>101.0233432221462</v>
+        <v>164.1772968638024</v>
       </c>
       <c r="C38" t="n">
-        <v>45.93043621542637</v>
+        <v>45.91096182065411</v>
       </c>
       <c r="D38" t="n">
-        <v>10.37987952049484</v>
+        <v>10.87829469942852</v>
       </c>
       <c r="E38" t="n">
-        <v>4.505075622707313</v>
+        <v>4.99363119512468</v>
       </c>
       <c r="F38" t="n">
-        <v>5.741221761372779</v>
+        <v>3.950550075461767</v>
       </c>
       <c r="G38" t="n">
-        <v>0.04456114675602837</v>
+        <v>0.1398033704546277</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.809561821796463</v>
+        <v>-0.4547606111868843</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8718896483080585</v>
+        <v>-0.6940131654886306</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9083307237653976</v>
+        <v>-0.629946265098102</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.2295045868193307</v>
+        <v>-0.01947781013540016</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.3733416509174253</v>
+        <v>-0.2155101819870174</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0009336420539919695</v>
+        <v>-0.06536270186379575</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>41.61173738827467</v>
+        <v>66.59674264908148</v>
       </c>
       <c r="B39" t="n">
-        <v>102.9569434301288</v>
+        <v>169.3234617432349</v>
       </c>
       <c r="C39" t="n">
-        <v>45.93220757802979</v>
+        <v>46.03344507385086</v>
       </c>
       <c r="D39" t="n">
-        <v>7.260899623909774</v>
+        <v>9.645288369978699</v>
       </c>
       <c r="E39" t="n">
-        <v>4.834629399490021</v>
+        <v>4.956477567243224</v>
       </c>
       <c r="F39" t="n">
-        <v>3.35934138865216</v>
+        <v>5.778428970352305</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2225711262656242</v>
+        <v>0.04046960982356505</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.2960672877385845</v>
+        <v>-0.79484008122127</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6247233490986415</v>
+        <v>-0.8636169349005504</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4825180014456315</v>
+        <v>-0.8989691583512054</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.02552789327550326</v>
+        <v>-0.05528845634928072</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.5263045154438918</v>
+        <v>-0.3495017913747055</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.001189316903371009</v>
+        <v>-0.09335887402305232</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39.43726447464938</v>
+        <v>83.12072219726464</v>
       </c>
       <c r="B40" t="n">
-        <v>104.3741608644288</v>
+        <v>173.8686854638804</v>
       </c>
       <c r="C40" t="n">
-        <v>45.92413506271384</v>
+        <v>46.03344507385086</v>
       </c>
       <c r="D40" t="n">
-        <v>7.57332091822375</v>
+        <v>8.597729331231195</v>
       </c>
       <c r="E40" t="n">
-        <v>3.708112372500109</v>
+        <v>4.955236341075946</v>
       </c>
       <c r="F40" t="n">
-        <v>3.190886022238437</v>
+        <v>7.936449582456653</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2739024052147236</v>
+        <v>0.01848408023067788</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1743174163904962</v>
+        <v>-0.8920173933048721</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.572589827336132</v>
+        <v>-0.9218356677536644</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3601581180359118</v>
+        <v>-0.9568083880846013</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.05192797146837565</v>
+        <v>-0.1408814159959489</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5118658805188718</v>
+        <v>-0.4672351456555105</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.414657995447877e-05</v>
+        <v>-0.09335887402305232</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>97.75408026768329</v>
+        <v>57.2650486507664</v>
       </c>
       <c r="B41" t="n">
-        <v>111.6034637376326</v>
+        <v>179.3624861105931</v>
       </c>
       <c r="C41" t="n">
-        <v>46.16066157754047</v>
+        <v>46.00726633048034</v>
       </c>
       <c r="D41" t="n">
-        <v>6.69843870175787</v>
+        <v>10.63721675730253</v>
       </c>
       <c r="E41" t="n">
-        <v>4.690906220113522</v>
+        <v>4.570795838177172</v>
       </c>
       <c r="F41" t="n">
-        <v>10.05208256006832</v>
+        <v>4.852455402364823</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01088416620114867</v>
+        <v>0.07080669321079158</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9401779433210483</v>
+        <v>-0.680273015489848</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9549917633651407</v>
+        <v>-0.8033011223069052</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9801706891583738</v>
+        <v>-0.8179162463236085</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.2225517442245157</v>
+        <v>-0.1005820532261528</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.6052297959857814</v>
+        <v>-0.2830134716367105</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.01909292667815785</v>
+        <v>-0.0873751612526491</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>52.59761301559543</v>
+        <v>39.46962119392788</v>
       </c>
       <c r="B42" t="n">
-        <v>108.2055592243305</v>
+        <v>54.02371570681271</v>
       </c>
       <c r="C42" t="n">
-        <v>45.9244784194745</v>
+        <v>35.69238005982186</v>
       </c>
       <c r="D42" t="n">
-        <v>6.69843870175787</v>
+        <v>5.007426391808701</v>
       </c>
       <c r="E42" t="n">
-        <v>4.958667587746389</v>
+        <v>4.952023035620901</v>
       </c>
       <c r="F42" t="n">
-        <v>4.467347392824553</v>
+        <v>3.251337970624297</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09217966997269514</v>
+        <v>0.2575722257114293</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6472829713318659</v>
+        <v>-0.06491671598655128</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.7890906924359989</v>
+        <v>-0.5288106714930458</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.7933211461866524</v>
+        <v>-0.248311761201115</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.03432770525789916</v>
+        <v>-0.03822516251583649</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5662098909495294</v>
+        <v>-0.460684773436813</v>
       </c>
       <c r="M42" t="n">
-        <v>-7.370599138985431e-05</v>
+        <v>-0.04275112440485923</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>41.70336518166453</v>
+        <v>39.46962119392788</v>
       </c>
       <c r="B43" t="n">
-        <v>103.7819096914561</v>
+        <v>54.02371570681271</v>
       </c>
       <c r="C43" t="n">
-        <v>45.93220757802979</v>
+        <v>35.69238005982186</v>
       </c>
       <c r="D43" t="n">
-        <v>7.264170036217597</v>
+        <v>5.007426391808701</v>
       </c>
       <c r="E43" t="n">
-        <v>4.798138023928155</v>
+        <v>4.983687540887594</v>
       </c>
       <c r="F43" t="n">
-        <v>3.369404354572546</v>
+        <v>3.251337970624297</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2207174534251461</v>
+        <v>0.2575722257114293</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.3006337450866564</v>
+        <v>-0.06491671598655128</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6267203208911547</v>
+        <v>-0.5288106714930458</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4869747789936154</v>
+        <v>-0.248311761201115</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.02878621380601813</v>
+        <v>-0.03822516251583649</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5269129296712898</v>
+        <v>-0.460684773436813</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.001189316903371009</v>
+        <v>-0.04275112440485923</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>39.85810572549022</v>
+        <v>57.11308726815663</v>
       </c>
       <c r="B44" t="n">
-        <v>101.4479544581243</v>
+        <v>182.9032495309026</v>
       </c>
       <c r="C44" t="n">
-        <v>45.92447560391316</v>
+        <v>40.13772794564289</v>
       </c>
       <c r="D44" t="n">
-        <v>7.37147789553078</v>
+        <v>10.8551529060516</v>
       </c>
       <c r="E44" t="n">
-        <v>4.804839534650839</v>
+        <v>4.761033690819753</v>
       </c>
       <c r="F44" t="n">
-        <v>3.199186534394864</v>
+        <v>4.838862543136885</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2625893992641692</v>
+        <v>0.07151763156155316</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.2001496194499986</v>
+        <v>-0.6777556031336426</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5834997524227311</v>
+        <v>-0.8020466338681919</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3866982100948511</v>
+        <v>-0.8160088030604435</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.01003798401806509</v>
+        <v>-0.008732409785214782</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5146602925091085</v>
+        <v>-0.2819307467856159</v>
       </c>
       <c r="M44" t="n">
-        <v>-7.329959903457546e-05</v>
+        <v>-0.03098878776964936</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45.52046158569344</v>
+        <v>73.27292973228894</v>
       </c>
       <c r="B45" t="n">
-        <v>111.6034637376326</v>
+        <v>177.6146073349214</v>
       </c>
       <c r="C45" t="n">
-        <v>45.94574321310817</v>
+        <v>45.9984573767518</v>
       </c>
       <c r="D45" t="n">
-        <v>7.057646029777744</v>
+        <v>9.552010834156608</v>
       </c>
       <c r="E45" t="n">
-        <v>4.875202308227296</v>
+        <v>4.735616191075591</v>
       </c>
       <c r="F45" t="n">
-        <v>3.750949683876696</v>
+        <v>6.641849939684509</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1580827772230022</v>
+        <v>0.02878232326304148</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4603601895718529</v>
+        <v>-0.8445517866865782</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6990352954305362</v>
+        <v>-0.892260605272533</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.6365330209881483</v>
+        <v>-0.9300430250862012</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.07662084982708094</v>
+        <v>-0.1440047967709932</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5522586863859569</v>
+        <v>-0.3970696243425587</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.002971039536409191</v>
+        <v>-0.08536168611469719</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50.55235586254665</v>
+        <v>83.12072219726464</v>
       </c>
       <c r="B46" t="n">
-        <v>108.4486731439305</v>
+        <v>173.9289287250631</v>
       </c>
       <c r="C46" t="n">
-        <v>45.92562903116303</v>
+        <v>46.03344507385086</v>
       </c>
       <c r="D46" t="n">
-        <v>6.801196454496667</v>
+        <v>8.597729331231195</v>
       </c>
       <c r="E46" t="n">
-        <v>4.781721876278753</v>
+        <v>4.955236341075946</v>
       </c>
       <c r="F46" t="n">
-        <v>4.31111915529642</v>
+        <v>7.936449582456653</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1065040232040745</v>
+        <v>0.01848408023067788</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6039405391881976</v>
+        <v>-0.8920173933048721</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7682716059817032</v>
+        <v>-0.9218356677536644</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7589975791113088</v>
+        <v>-0.9568083880846013</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.1545665150253658</v>
+        <v>-0.1408814159959489</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.5856707762719847</v>
+        <v>-0.4672351456555105</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.00023978292537891</v>
+        <v>-0.09335887402305232</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>64.13630984390682</v>
+        <v>66.59674264908148</v>
       </c>
       <c r="B47" t="n">
-        <v>103.5773758841167</v>
+        <v>193.3402319309811</v>
       </c>
       <c r="C47" t="n">
-        <v>45.92418029945001</v>
+        <v>46.03344507385086</v>
       </c>
       <c r="D47" t="n">
-        <v>9.33089725597234</v>
+        <v>9.645288369978699</v>
       </c>
       <c r="E47" t="n">
-        <v>4.737742497729563</v>
+        <v>2.118868152864876</v>
       </c>
       <c r="F47" t="n">
-        <v>5.428970480822094</v>
+        <v>5.778428970352305</v>
       </c>
       <c r="G47" t="n">
-        <v>0.04708595939853219</v>
+        <v>0.04046960982356505</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7999977241008019</v>
+        <v>-0.79484008122127</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8666615126794547</v>
+        <v>-0.8636169349005504</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.902235905836465</v>
+        <v>-0.8989691583512054</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.02684539431475683</v>
+        <v>-0.05528845634928072</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.3648964878257581</v>
+        <v>-0.3495017913747055</v>
       </c>
       <c r="M47" t="n">
-        <v>-3.067595778259806e-05</v>
+        <v>-0.09335887402305232</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>44.77263330966479</v>
+        <v>49.67481186441836</v>
       </c>
       <c r="B48" t="n">
-        <v>113.6003031566467</v>
+        <v>179.5854529462824</v>
       </c>
       <c r="C48" t="n">
-        <v>45.92755631930124</v>
+        <v>46.00726633048034</v>
       </c>
       <c r="D48" t="n">
-        <v>6.876796612205101</v>
+        <v>10.63721675730253</v>
       </c>
       <c r="E48" t="n">
-        <v>4.856023383918397</v>
+        <v>4.570795838177172</v>
       </c>
       <c r="F48" t="n">
-        <v>3.636387253466336</v>
+        <v>4.087447246689183</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1680859445517203</v>
+        <v>0.1205026918172003</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.4334499131961582</v>
+        <v>-0.513907076216976</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6865349629140681</v>
+        <v>-0.7222941039598727</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.612289786633847</v>
+        <v>-0.6823716670461182</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.005429266407146641</v>
+        <v>-0.001421382125063448</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5472930602811078</v>
+        <v>-0.2289330345339808</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0005179637470220229</v>
+        <v>-0.0873751612526491</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>61.20238341641294</v>
+        <v>46.36682029753885</v>
       </c>
       <c r="B49" t="n">
-        <v>106.8347058940967</v>
+        <v>157.1863532961234</v>
       </c>
       <c r="C49" t="n">
-        <v>45.93067645908275</v>
+        <v>46.10052407421429</v>
       </c>
       <c r="D49" t="n">
-        <v>9.563350121097496</v>
+        <v>10.85342405119466</v>
       </c>
       <c r="E49" t="n">
-        <v>4.840229562923257</v>
+        <v>4.865500362866547</v>
       </c>
       <c r="F49" t="n">
-        <v>5.120014810045902</v>
+        <v>3.827470804615323</v>
       </c>
       <c r="G49" t="n">
-        <v>0.05593989140014648</v>
+        <v>0.156867539958967</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.7706514031444932</v>
+        <v>-0.4036610273139219</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8504692519298545</v>
+        <v>-0.6702626473717823</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.8827685536258909</v>
+        <v>-0.583137303172108</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.02408977491771351</v>
+        <v>-0.001137182178063368</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.3430579041056531</v>
+        <v>-0.2053635946199643</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0009683183311926616</v>
+        <v>-0.1086912169632673</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>45.08251378847866</v>
+        <v>73.27292973228894</v>
       </c>
       <c r="B50" t="n">
-        <v>103.0599132596767</v>
+        <v>177.6146073349214</v>
       </c>
       <c r="C50" t="n">
-        <v>45.92565541665721</v>
+        <v>45.9984573767518</v>
       </c>
       <c r="D50" t="n">
-        <v>7.07843275415425</v>
+        <v>9.552010834156608</v>
       </c>
       <c r="E50" t="n">
-        <v>4.991213279883372</v>
+        <v>2.056300900435678</v>
       </c>
       <c r="F50" t="n">
-        <v>3.704376356833584</v>
+        <v>6.641849939684509</v>
       </c>
       <c r="G50" t="n">
-        <v>0.163982973290587</v>
+        <v>0.02878232326304148</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4447171910927699</v>
+        <v>-0.8445517866865782</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6917276584522951</v>
+        <v>-0.892260605272533</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.6224664451305839</v>
+        <v>-0.9300430250862012</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.06963646309964827</v>
+        <v>-0.1440047967709932</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.5493506858674964</v>
+        <v>-0.3970696243425587</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0002435913535568472</v>
+        <v>-0.08536168611469719</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96.71785295616942</v>
+        <v>94.69583592042756</v>
       </c>
       <c r="B51" t="n">
-        <v>131.14547984916</v>
+        <v>179.100524777032</v>
       </c>
       <c r="C51" t="n">
-        <v>45.92422282810497</v>
+        <v>48.07738769941636</v>
       </c>
       <c r="D51" t="n">
-        <v>6.991940218009444</v>
+        <v>7.396291409247471</v>
       </c>
       <c r="E51" t="n">
-        <v>4.74890460733754</v>
+        <v>4.90940642803762</v>
       </c>
       <c r="F51" t="n">
-        <v>9.906329033246752</v>
+        <v>9.731622134943965</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01127877468529627</v>
+        <v>0.01190802632236695</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.9383558982087836</v>
+        <v>-0.9255138738034603</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9536546075432057</v>
+        <v>-0.9444416406710238</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9793701435149668</v>
+        <v>-0.9735506482238688</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.2499991183099198</v>
+        <v>-0.1866187824248996</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5974891057127041</v>
+        <v>-0.5497078309330463</v>
       </c>
       <c r="M51" t="n">
-        <v>-3.68144567143569e-05</v>
+        <v>-0.09863560033351003</v>
       </c>
     </row>
   </sheetData>
